--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_individual_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_individual_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.008511962878429835</v>
       </c>
       <c r="C2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>43479046</v>
+        <v>3850650</v>
       </c>
       <c r="L2" t="n">
-        <v>23380333</v>
+        <v>1797295</v>
       </c>
       <c r="M2" t="n">
-        <v>5482487</v>
+        <v>373323</v>
       </c>
       <c r="N2" t="n">
-        <v>161204</v>
+        <v>8838</v>
       </c>
       <c r="O2" t="n">
-        <v>3350937</v>
+        <v>241060</v>
       </c>
       <c r="P2" t="n">
-        <v>1193287</v>
+        <v>89760</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999390244483948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8445903062820435</v>
+        <v>0.7469624876976013</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7120702862739563</v>
+        <v>0.5482860803604126</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6359361410140991</v>
+        <v>0.4323960840702057</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2184780091047287</v>
+        <v>0.1214644983410835</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6721982359886169</v>
+        <v>0.4842292964458466</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7930972576141357</v>
+        <v>0.6017336249351501</v>
       </c>
       <c r="X2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="AG2" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AH2" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AI2" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559409618377686</v>
+        <v>0.9546809196472168</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116660952568054</v>
+        <v>0.9128581881523132</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582287430763245</v>
+        <v>0.8581860065460205</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617533564567566</v>
+        <v>0.6609027981758118</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.902009129524231</v>
+        <v>0.901951789855957</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002039737086905555</v>
       </c>
       <c r="C3" t="n">
-        <v>3622</v>
+        <v>363</v>
       </c>
       <c r="D3" t="n">
-        <v>43479046</v>
+        <v>3850650</v>
       </c>
       <c r="E3" t="n">
-        <v>6354698</v>
+        <v>1042201</v>
       </c>
       <c r="F3" t="n">
-        <v>205543</v>
+        <v>56412</v>
       </c>
       <c r="G3" t="n">
-        <v>13480</v>
+        <v>3531</v>
       </c>
       <c r="H3" t="n">
-        <v>18334</v>
+        <v>6453</v>
       </c>
       <c r="I3" t="n">
-        <v>1017</v>
+        <v>502</v>
       </c>
       <c r="J3" t="n">
-        <v>100162370</v>
+        <v>10016237</v>
       </c>
       <c r="K3" t="n">
-        <v>105219853</v>
+        <v>10065060</v>
       </c>
       <c r="L3" t="n">
-        <v>121032708</v>
+        <v>11529739</v>
       </c>
       <c r="M3" t="n">
-        <v>150804806</v>
+        <v>14897685</v>
       </c>
       <c r="N3" t="n">
-        <v>161825790</v>
+        <v>16175868</v>
       </c>
       <c r="O3" t="n">
-        <v>156561464</v>
+        <v>15560929</v>
       </c>
       <c r="P3" t="n">
-        <v>161050083</v>
+        <v>16076386</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.868265688419342</v>
+        <v>0.7763231992721558</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7126125693321228</v>
+        <v>0.5414955019950867</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5862022042274475</v>
+        <v>0.3963695168495178</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1804056614637375</v>
+        <v>0.09840994328260422</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6569910645484924</v>
+        <v>0.4709040224552155</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6168091297149658</v>
+        <v>0.4631459414958954</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="Z3" t="n">
-        <v>1972670</v>
+        <v>194702</v>
       </c>
       <c r="AA3" t="n">
-        <v>84826</v>
+        <v>8398</v>
       </c>
       <c r="AB3" t="n">
-        <v>68106</v>
+        <v>6808</v>
       </c>
       <c r="AC3" t="n">
-        <v>280</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100166220</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>111010280</v>
+        <v>11143996</v>
       </c>
       <c r="AG3" t="n">
-        <v>127594505</v>
+        <v>12722349</v>
       </c>
       <c r="AH3" t="n">
-        <v>152619092</v>
+        <v>15254456</v>
       </c>
       <c r="AI3" t="n">
-        <v>162100491</v>
+        <v>16209376</v>
       </c>
       <c r="AJ3" t="n">
-        <v>157696105</v>
+        <v>15767551</v>
       </c>
       <c r="AK3" t="n">
-        <v>161228809</v>
+        <v>16122526</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575406908988953</v>
+        <v>0.9576725363731384</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097784161567688</v>
+        <v>0.9093356132507324</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85721355676651</v>
+        <v>0.8563846349716187</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.661096453666687</v>
+        <v>0.6600859761238098</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014128446578979</v>
+        <v>0.9010214805603027</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>7425511</v>
+        <v>1183789</v>
       </c>
       <c r="E4" t="n">
-        <v>23380333</v>
+        <v>1797295</v>
       </c>
       <c r="F4" t="n">
-        <v>1692761</v>
+        <v>263357</v>
       </c>
       <c r="G4" t="n">
-        <v>71305</v>
+        <v>14683</v>
       </c>
       <c r="H4" t="n">
-        <v>217744</v>
+        <v>53476</v>
       </c>
       <c r="I4" t="n">
-        <v>21666</v>
+        <v>6532</v>
       </c>
       <c r="J4" t="n">
-        <v>3850</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>8000407</v>
+        <v>1304428</v>
       </c>
       <c r="L4" t="n">
-        <v>9453972</v>
+        <v>1480729</v>
       </c>
       <c r="M4" t="n">
-        <v>3138641</v>
+        <v>490059</v>
       </c>
       <c r="N4" t="n">
-        <v>576646</v>
+        <v>63924</v>
       </c>
       <c r="O4" t="n">
-        <v>1634106</v>
+        <v>256762</v>
       </c>
       <c r="P4" t="n">
-        <v>311304</v>
+        <v>59409</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999695420265198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8562642931938171</v>
+        <v>0.7613598704338074</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7123413681983948</v>
+        <v>0.5448697209358215</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6100572347640991</v>
+        <v>0.4135997295379639</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1976248919963837</v>
+        <v>0.1087285503745079</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6645076870918274</v>
+        <v>0.4774737060070038</v>
       </c>
       <c r="W4" t="n">
-        <v>0.693932056427002</v>
+        <v>0.5234216451644897</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2063963</v>
+        <v>210743</v>
       </c>
       <c r="Z4" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AA4" t="n">
-        <v>828823</v>
+        <v>83377</v>
       </c>
       <c r="AB4" t="n">
-        <v>55262</v>
+        <v>5608</v>
       </c>
       <c r="AC4" t="n">
-        <v>11381</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2209980</v>
+        <v>225492</v>
       </c>
       <c r="AG4" t="n">
-        <v>2892175</v>
+        <v>288119</v>
       </c>
       <c r="AH4" t="n">
-        <v>1324355</v>
+        <v>133288</v>
       </c>
       <c r="AI4" t="n">
-        <v>301945</v>
+        <v>30416</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499465</v>
+        <v>50140</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567400813102722</v>
+        <v>0.956174373626709</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107212424278259</v>
+        <v>0.9110934734344482</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577207922935486</v>
+        <v>0.8572843670845032</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614247560501099</v>
+        <v>0.6604941487312317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017109274864197</v>
+        <v>0.9014863967895508</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>403718</v>
+        <v>89530</v>
       </c>
       <c r="E5" t="n">
-        <v>2549893</v>
+        <v>332290</v>
       </c>
       <c r="F5" t="n">
-        <v>5482487</v>
+        <v>373323</v>
       </c>
       <c r="G5" t="n">
-        <v>176101</v>
+        <v>21148</v>
       </c>
       <c r="H5" t="n">
-        <v>670939</v>
+        <v>109676</v>
       </c>
       <c r="I5" t="n">
-        <v>69415</v>
+        <v>15889</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6596694</v>
+        <v>1109462</v>
       </c>
       <c r="L5" t="n">
-        <v>9428987</v>
+        <v>1521837</v>
       </c>
       <c r="M5" t="n">
-        <v>3870066</v>
+        <v>568533</v>
       </c>
       <c r="N5" t="n">
-        <v>732360</v>
+        <v>80970</v>
       </c>
       <c r="O5" t="n">
-        <v>1749493</v>
+        <v>270849</v>
       </c>
       <c r="P5" t="n">
-        <v>741326</v>
+        <v>104045</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999763965606689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9106095433235168</v>
+        <v>0.8521770238876343</v>
       </c>
       <c r="S5" t="n">
-        <v>0.88436359167099</v>
+        <v>0.8161274194717407</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9570797681808472</v>
+        <v>0.9351734519004822</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9919838309288025</v>
+        <v>0.9911268949508667</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9792793393135071</v>
+        <v>0.9676898717880249</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9935538768768311</v>
+        <v>0.9899903535842896</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80454</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>857060</v>
+        <v>87176</v>
       </c>
       <c r="AA5" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AB5" t="n">
-        <v>99758</v>
+        <v>10039</v>
       </c>
       <c r="AC5" t="n">
-        <v>291816</v>
+        <v>29297</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2126182</v>
+        <v>209949</v>
       </c>
       <c r="AG5" t="n">
-        <v>2960109</v>
+        <v>300927</v>
       </c>
       <c r="AH5" t="n">
-        <v>1335418</v>
+        <v>135265</v>
       </c>
       <c r="AI5" t="n">
-        <v>302832</v>
+        <v>30527</v>
       </c>
       <c r="AJ5" t="n">
-        <v>502837</v>
+        <v>50668</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734460115432739</v>
+        <v>0.9733342528343201</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641615152359009</v>
+        <v>0.963927686214447</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837119579315186</v>
+        <v>0.9835542440414429</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962964653968811</v>
+        <v>0.9962679147720337</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938620328903198</v>
+        <v>0.993826687335968</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983729124069214</v>
+        <v>0.9983675479888916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>140146</v>
+        <v>18874</v>
       </c>
       <c r="E6" t="n">
-        <v>208804</v>
+        <v>24415</v>
       </c>
       <c r="F6" t="n">
-        <v>272155</v>
+        <v>23365</v>
       </c>
       <c r="G6" t="n">
-        <v>161204</v>
+        <v>8838</v>
       </c>
       <c r="H6" t="n">
-        <v>102223</v>
+        <v>12514</v>
       </c>
       <c r="I6" t="n">
-        <v>8824</v>
+        <v>1781</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65084</v>
+        <v>6593</v>
       </c>
       <c r="Z6" t="n">
-        <v>53535</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>109471</v>
+        <v>11081</v>
       </c>
       <c r="AB6" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AC6" t="n">
-        <v>69932</v>
+        <v>7022</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>29656</v>
+        <v>11567</v>
       </c>
       <c r="E7" t="n">
-        <v>311745</v>
+        <v>73194</v>
       </c>
       <c r="F7" t="n">
-        <v>901578</v>
+        <v>130275</v>
       </c>
       <c r="G7" t="n">
-        <v>296132</v>
+        <v>21108</v>
       </c>
       <c r="H7" t="n">
-        <v>3350937</v>
+        <v>241060</v>
       </c>
       <c r="I7" t="n">
-        <v>210382</v>
+        <v>34705</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8100</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>297921</v>
+        <v>30099</v>
       </c>
       <c r="AB7" t="n">
-        <v>76159</v>
+        <v>7694</v>
       </c>
       <c r="AC7" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1376</v>
+        <v>668</v>
       </c>
       <c r="E8" t="n">
-        <v>28832</v>
+        <v>8629</v>
       </c>
       <c r="F8" t="n">
-        <v>66604</v>
+        <v>16650</v>
       </c>
       <c r="G8" t="n">
-        <v>19628</v>
+        <v>3454</v>
       </c>
       <c r="H8" t="n">
-        <v>624866</v>
+        <v>74643</v>
       </c>
       <c r="I8" t="n">
-        <v>1193287</v>
+        <v>89760</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
